--- a/files/NRLW_futures_sim.xlsx
+++ b/files/NRLW_futures_sim.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t xml:space="preserve">team_key</t>
   </si>
@@ -74,6 +74,12 @@
     <t xml:space="preserve">venue</t>
   </si>
   <si>
+    <t xml:space="preserve">sydneyroosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sydney Roosters</t>
+  </si>
+  <si>
     <t xml:space="preserve">goldcoasttitans</t>
   </si>
   <si>
@@ -86,10 +92,10 @@
     <t xml:space="preserve">Newcastle Knights</t>
   </si>
   <si>
-    <t xml:space="preserve">sydneyroosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sydney Roosters</t>
+    <t xml:space="preserve">brisbanebroncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brisbane Broncos</t>
   </si>
   <si>
     <t xml:space="preserve">canberraraiders</t>
@@ -104,10 +110,10 @@
     <t xml:space="preserve">Wests Tigers</t>
   </si>
   <si>
-    <t xml:space="preserve">brisbanebroncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brisbane Broncos</t>
+    <t xml:space="preserve">parramattaeels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parramatta Eels</t>
   </si>
   <si>
     <t xml:space="preserve">warriors</t>
@@ -122,28 +128,28 @@
     <t xml:space="preserve">Canterbury-Bankstown Bulldogs</t>
   </si>
   <si>
+    <t xml:space="preserve">cronullasharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cronulla-Sutherland Sharks</t>
+  </si>
+  <si>
     <t xml:space="preserve">nqcowboys</t>
   </si>
   <si>
     <t xml:space="preserve">North Queensland Cowboys</t>
   </si>
   <si>
-    <t xml:space="preserve">parramattaeels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parramatta Eels</t>
+    <t xml:space="preserve">tba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBA</t>
   </si>
   <si>
     <t xml:space="preserve">stgeorgeillawarradragons</t>
   </si>
   <si>
     <t xml:space="preserve">St George-Illawarra Dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronullasharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cronulla-Sutherland Sharks</t>
   </si>
 </sst>
 </file>
@@ -564,13 +570,13 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
@@ -593,22 +599,22 @@
       </c>
       <c r="M2"/>
       <c r="N2" t="n">
-        <v>0.1</v>
+        <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>1818.18</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>48.9</v>
+        <v>74.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.04</v>
+        <v>1.34</v>
       </c>
       <c r="R2" t="n">
-        <v>29.5</v>
+        <v>49.6</v>
       </c>
       <c r="S2" t="n">
-        <v>3.39</v>
+        <v>2.02</v>
       </c>
       <c r="T2"/>
     </row>
@@ -620,24 +626,24 @@
         <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3"/>
+        <v>100</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
       <c r="H3" t="n">
-        <v>100</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I3"/>
       <c r="J3" t="n">
         <v>100</v>
       </c>
@@ -653,16 +659,16 @@
       </c>
       <c r="O3"/>
       <c r="P3" t="n">
-        <v>45.8</v>
+        <v>63.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.18</v>
+        <v>1.58</v>
       </c>
       <c r="R3" t="n">
-        <v>25.7</v>
+        <v>27.3</v>
       </c>
       <c r="S3" t="n">
-        <v>3.9</v>
+        <v>3.66</v>
       </c>
       <c r="T3"/>
     </row>
@@ -674,24 +680,24 @@
         <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>5.7</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>5.7</v>
       </c>
       <c r="F4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G4"/>
       <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4"/>
+        <v>100</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
       <c r="J4" t="n">
         <v>100</v>
       </c>
@@ -703,22 +709,20 @@
       </c>
       <c r="M4"/>
       <c r="N4" t="n">
-        <v>99.9</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O4"/>
       <c r="P4" t="n">
-        <v>38.3</v>
+        <v>19.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.61</v>
+        <v>5.18</v>
       </c>
       <c r="R4" t="n">
-        <v>16.7</v>
+        <v>9.2</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>10.87</v>
       </c>
       <c r="T4"/>
     </row>
@@ -730,24 +734,24 @@
         <v>27</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>5.3</v>
+        <v>8.3</v>
       </c>
       <c r="E5" t="n">
-        <v>5.3</v>
+        <v>8.3</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5"/>
+        <v>100</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
       <c r="H5" t="n">
-        <v>100</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I5"/>
       <c r="J5" t="n">
         <v>100</v>
       </c>
@@ -763,16 +767,16 @@
       </c>
       <c r="O5"/>
       <c r="P5" t="n">
-        <v>31.1</v>
+        <v>20.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.21</v>
+        <v>4.93</v>
       </c>
       <c r="R5" t="n">
-        <v>11.8</v>
+        <v>6.7</v>
       </c>
       <c r="S5" t="n">
-        <v>8.51</v>
+        <v>14.87</v>
       </c>
       <c r="T5"/>
     </row>
@@ -784,24 +788,26 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>7.7</v>
+        <v>6.3</v>
       </c>
       <c r="E6" t="n">
-        <v>7.7</v>
+        <v>6.3</v>
       </c>
       <c r="F6" t="n">
-        <v>100</v>
+        <v>29.1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>3.43</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6"/>
+        <v>70.9</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.41</v>
+      </c>
       <c r="J6" t="n">
         <v>100</v>
       </c>
@@ -817,16 +823,16 @@
       </c>
       <c r="O6"/>
       <c r="P6" t="n">
-        <v>20</v>
+        <v>11.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>8.59</v>
       </c>
       <c r="R6" t="n">
-        <v>9.3</v>
+        <v>3.9</v>
       </c>
       <c r="S6" t="n">
-        <v>10.7</v>
+        <v>25.84</v>
       </c>
       <c r="T6"/>
     </row>
@@ -841,21 +847,23 @@
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="E7" t="n">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="F7" t="n">
-        <v>100</v>
+        <v>70.9</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>1.41</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7"/>
+        <v>29.1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.43</v>
+      </c>
       <c r="J7" t="n">
         <v>100</v>
       </c>
@@ -871,16 +879,16 @@
       </c>
       <c r="O7"/>
       <c r="P7" t="n">
-        <v>15.9</v>
+        <v>11.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.3</v>
+        <v>9</v>
       </c>
       <c r="R7" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="S7" t="n">
-        <v>14.2</v>
+        <v>29.9</v>
       </c>
       <c r="T7"/>
     </row>
@@ -895,10 +903,10 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -927,15 +935,11 @@
       <c r="P8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>20000</v>
-      </c>
+      <c r="Q8"/>
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="n">
-        <v>20000</v>
-      </c>
+      <c r="S8"/>
       <c r="T8"/>
     </row>
     <row r="9">
@@ -946,7 +950,7 @@
         <v>35</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
         <v>4</v>
@@ -965,17 +969,15 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>62.3</v>
+        <v>100</v>
       </c>
       <c r="K9" t="n">
-        <v>1.61</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2.65</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M9"/>
       <c r="N9" t="n">
         <v>0</v>
       </c>
@@ -1001,10 +1003,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1017,16 +1019,14 @@
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K10" t="n">
-        <v>54.05</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K10"/>
       <c r="L10" t="n">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="M10" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1053,10 +1053,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1069,16 +1069,14 @@
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>35.9</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2.79</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K11"/>
       <c r="L11" t="n">
-        <v>64.1</v>
+        <v>100</v>
       </c>
       <c r="M11" t="n">
-        <v>1.56</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1102,13 +1100,13 @@
         <v>41</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1152,13 +1150,13 @@
         <v>43</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1193,6 +1191,56 @@
       </c>
       <c r="S13"/>
       <c r="T13"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14"/>
+      <c r="H14" t="n">
+        <v>100</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14"/>
+      <c r="L14" t="n">
+        <v>100</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14"/>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14"/>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14"/>
+      <c r="T14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/files/NRLW_futures_sim.xlsx
+++ b/files/NRLW_futures_sim.xlsx
@@ -74,16 +74,28 @@
     <t xml:space="preserve">venue</t>
   </si>
   <si>
+    <t xml:space="preserve">goldcoasttitans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold Coast Titans</t>
+  </si>
+  <si>
     <t xml:space="preserve">sydneyroosters</t>
   </si>
   <si>
     <t xml:space="preserve">Sydney Roosters</t>
   </si>
   <si>
-    <t xml:space="preserve">goldcoasttitans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gold Coast Titans</t>
+    <t xml:space="preserve">canberraraiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canberra Raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbanebroncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brisbane Broncos</t>
   </si>
   <si>
     <t xml:space="preserve">newcastleknights</t>
@@ -92,18 +104,6 @@
     <t xml:space="preserve">Newcastle Knights</t>
   </si>
   <si>
-    <t xml:space="preserve">brisbanebroncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brisbane Broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberraraiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canberra Raiders</t>
-  </si>
-  <si>
     <t xml:space="preserve">weststigers</t>
   </si>
   <si>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">North Queensland Cowboys</t>
   </si>
   <si>
+    <t xml:space="preserve">stgeorgeillawarradragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">St George-Illawarra Dragons</t>
+  </si>
+  <si>
     <t xml:space="preserve">tba</t>
   </si>
   <si>
     <t xml:space="preserve">TBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stgeorgeillawarradragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">St George-Illawarra Dragons</t>
   </si>
 </sst>
 </file>
@@ -570,13 +570,13 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
@@ -599,22 +599,20 @@
       </c>
       <c r="M2"/>
       <c r="N2" t="n">
-        <v>100</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O2"/>
       <c r="P2" t="n">
-        <v>74.4</v>
+        <v>50.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.34</v>
+        <v>1.99</v>
       </c>
       <c r="R2" t="n">
-        <v>49.6</v>
+        <v>27.9</v>
       </c>
       <c r="S2" t="n">
-        <v>2.02</v>
+        <v>3.59</v>
       </c>
       <c r="T2"/>
     </row>
@@ -626,13 +624,13 @@
         <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="F3" t="n">
         <v>100</v>
@@ -655,20 +653,22 @@
       </c>
       <c r="M3"/>
       <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3"/>
+        <v>100</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
       <c r="P3" t="n">
-        <v>63.2</v>
+        <v>54.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.58</v>
+        <v>1.84</v>
       </c>
       <c r="R3" t="n">
-        <v>27.3</v>
+        <v>26.2</v>
       </c>
       <c r="S3" t="n">
-        <v>3.66</v>
+        <v>3.82</v>
       </c>
       <c r="T3"/>
     </row>
@@ -680,24 +680,24 @@
         <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>5.7</v>
+        <v>7.9</v>
       </c>
       <c r="E4" t="n">
-        <v>5.7</v>
+        <v>7.9</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4"/>
+        <v>100</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
       <c r="H4" t="n">
-        <v>100</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I4"/>
       <c r="J4" t="n">
         <v>100</v>
       </c>
@@ -713,16 +713,16 @@
       </c>
       <c r="O4"/>
       <c r="P4" t="n">
-        <v>19.3</v>
+        <v>41.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.18</v>
+        <v>2.39</v>
       </c>
       <c r="R4" t="n">
-        <v>9.2</v>
+        <v>23.5</v>
       </c>
       <c r="S4" t="n">
-        <v>10.87</v>
+        <v>4.25</v>
       </c>
       <c r="T4"/>
     </row>
@@ -734,13 +734,13 @@
         <v>27</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>8.3</v>
+        <v>9.3</v>
       </c>
       <c r="E5" t="n">
-        <v>8.3</v>
+        <v>9.3</v>
       </c>
       <c r="F5" t="n">
         <v>100</v>
@@ -767,16 +767,16 @@
       </c>
       <c r="O5"/>
       <c r="P5" t="n">
-        <v>20.3</v>
+        <v>30.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.93</v>
+        <v>3.28</v>
       </c>
       <c r="R5" t="n">
-        <v>6.7</v>
+        <v>14.5</v>
       </c>
       <c r="S5" t="n">
-        <v>14.87</v>
+        <v>6.91</v>
       </c>
       <c r="T5"/>
     </row>
@@ -788,25 +788,23 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3.43</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G6"/>
       <c r="H6" t="n">
-        <v>70.9</v>
+        <v>100</v>
       </c>
       <c r="I6" t="n">
-        <v>1.41</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>100</v>
@@ -823,16 +821,16 @@
       </c>
       <c r="O6"/>
       <c r="P6" t="n">
-        <v>11.6</v>
+        <v>16.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.59</v>
+        <v>6.17</v>
       </c>
       <c r="R6" t="n">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="S6" t="n">
-        <v>25.84</v>
+        <v>16.71</v>
       </c>
       <c r="T6"/>
     </row>
@@ -847,22 +845,20 @@
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="F7" t="n">
-        <v>70.9</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.41</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G7"/>
       <c r="H7" t="n">
-        <v>29.1</v>
+        <v>100</v>
       </c>
       <c r="I7" t="n">
-        <v>3.43</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>100</v>
@@ -879,16 +875,16 @@
       </c>
       <c r="O7"/>
       <c r="P7" t="n">
-        <v>11.1</v>
+        <v>7.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>9</v>
+        <v>14.13</v>
       </c>
       <c r="R7" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>29.9</v>
+        <v>49.75</v>
       </c>
       <c r="T7"/>
     </row>
@@ -1150,13 +1146,13 @@
         <v>43</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1200,13 +1196,13 @@
         <v>45</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>

--- a/files/NRLW_futures_sim.xlsx
+++ b/files/NRLW_futures_sim.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t xml:space="preserve">team_key</t>
   </si>
@@ -74,30 +74,30 @@
     <t xml:space="preserve">venue</t>
   </si>
   <si>
+    <t xml:space="preserve">sydneyroosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sydney Roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbanebroncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brisbane Broncos</t>
+  </si>
+  <si>
     <t xml:space="preserve">goldcoasttitans</t>
   </si>
   <si>
     <t xml:space="preserve">Gold Coast Titans</t>
   </si>
   <si>
-    <t xml:space="preserve">sydneyroosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sydney Roosters</t>
-  </si>
-  <si>
     <t xml:space="preserve">canberraraiders</t>
   </si>
   <si>
     <t xml:space="preserve">Canberra Raiders</t>
   </si>
   <si>
-    <t xml:space="preserve">brisbanebroncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brisbane Broncos</t>
-  </si>
-  <si>
     <t xml:space="preserve">newcastleknights</t>
   </si>
   <si>
@@ -144,12 +144,6 @@
   </si>
   <si>
     <t xml:space="preserve">St George-Illawarra Dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TBA</t>
   </si>
 </sst>
 </file>
@@ -570,13 +564,13 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>10.7</v>
+        <v>12.4</v>
       </c>
       <c r="E2" t="n">
-        <v>10.7</v>
+        <v>12.4</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
@@ -599,20 +593,22 @@
       </c>
       <c r="M2"/>
       <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2"/>
+        <v>100</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
       <c r="P2" t="n">
-        <v>50.2</v>
+        <v>71.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.99</v>
+        <v>1.41</v>
       </c>
       <c r="R2" t="n">
-        <v>27.9</v>
+        <v>40.5</v>
       </c>
       <c r="S2" t="n">
-        <v>3.59</v>
+        <v>2.47</v>
       </c>
       <c r="T2"/>
     </row>
@@ -624,13 +620,13 @@
         <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>10.6</v>
       </c>
       <c r="E3" t="n">
-        <v>11.1</v>
+        <v>10.6</v>
       </c>
       <c r="F3" t="n">
         <v>100</v>
@@ -653,22 +649,20 @@
       </c>
       <c r="M3"/>
       <c r="N3" t="n">
-        <v>100</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O3"/>
       <c r="P3" t="n">
-        <v>54.2</v>
+        <v>60.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="R3" t="n">
-        <v>26.2</v>
+        <v>31.7</v>
       </c>
       <c r="S3" t="n">
-        <v>3.82</v>
+        <v>3.16</v>
       </c>
       <c r="T3"/>
     </row>
@@ -680,13 +674,13 @@
         <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>7.9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>7.9</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
         <v>100</v>
@@ -713,16 +707,16 @@
       </c>
       <c r="O4"/>
       <c r="P4" t="n">
-        <v>41.8</v>
+        <v>28</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.39</v>
+        <v>3.57</v>
       </c>
       <c r="R4" t="n">
-        <v>23.5</v>
+        <v>13.1</v>
       </c>
       <c r="S4" t="n">
-        <v>4.25</v>
+        <v>7.64</v>
       </c>
       <c r="T4"/>
     </row>
@@ -734,13 +728,13 @@
         <v>27</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>9.3</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>9.3</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
         <v>100</v>
@@ -767,16 +761,16 @@
       </c>
       <c r="O5"/>
       <c r="P5" t="n">
-        <v>30.5</v>
+        <v>22.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.28</v>
+        <v>4.45</v>
       </c>
       <c r="R5" t="n">
-        <v>14.5</v>
+        <v>8.6</v>
       </c>
       <c r="S5" t="n">
-        <v>6.91</v>
+        <v>11.68</v>
       </c>
       <c r="T5"/>
     </row>
@@ -821,16 +815,16 @@
       </c>
       <c r="O6"/>
       <c r="P6" t="n">
-        <v>16.2</v>
+        <v>11.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.17</v>
+        <v>8.84</v>
       </c>
       <c r="R6" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="S6" t="n">
-        <v>16.71</v>
+        <v>22.75</v>
       </c>
       <c r="T6"/>
     </row>
@@ -875,16 +869,16 @@
       </c>
       <c r="O7"/>
       <c r="P7" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.13</v>
+        <v>14.58</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="S7" t="n">
-        <v>49.75</v>
+        <v>56.98</v>
       </c>
       <c r="T7"/>
     </row>
@@ -1187,56 +1181,6 @@
       </c>
       <c r="S13"/>
       <c r="T13"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14"/>
-      <c r="H14" t="n">
-        <v>100</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14"/>
-      <c r="L14" t="n">
-        <v>100</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14"/>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14"/>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14"/>
-      <c r="T14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
